--- a/static/office_ops/monthly_outlook_goals_template_2026.xlsx
+++ b/static/office_ops/monthly_outlook_goals_template_2026.xlsx
@@ -1344,7 +1344,7 @@
         <v/>
       </c>
       <c r="N11" s="23" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
